--- a/stories/arbres/ATOM-TMP.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B29"/>
+  <dimension ref="A1:B30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -602,7 +602,6 @@
           <t>secondary_lessons</t>
         </is>
       </c>
-      <c r="B10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -819,6 +818,18 @@
       <c r="B29" t="inlineStr">
         <is>
           <t>xlsx-arbre-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>voice_cast</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>voix-roles-v1</t>
         </is>
       </c>
     </row>
@@ -833,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AV6"/>
+  <dimension ref="A1:AW6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1127,6 +1138,11 @@
           <t>notes</t>
         </is>
       </c>
+      <c r="AW1" t="inlineStr">
+        <is>
+          <t>script</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1151,7 +1167,7 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hermine est dans l'entrée. Papa ouvre la porte. L'air est froid. Papa dit : froid, manteau. Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence. Papa dit : pluie, bottes. Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip. Hermine dit : froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble. Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
+          <t>Hermine est dans l'entrée. Papa ouvre la porte. L'air est froid. Froid, manteau. Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence. Pluie, bottes. Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip. Froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble. Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
@@ -1289,6 +1305,17 @@
         <v>8</v>
       </c>
       <c r="AV2" s="2" t="inlineStr"/>
+      <c r="AW2" t="inlineStr">
+        <is>
+          <t>narrateur|Hermine est dans l'entrée. Papa ouvre la porte. L'air est froid.
+papa|Froid, manteau.
+narrateur|Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence.
+papa|Pluie, bottes.
+narrateur|Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip.
+enfant-f|Froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble.
+narrateur|Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1469,6 +1496,11 @@
       <c r="AV3" s="2" t="inlineStr">
         <is>
           <t>question d'écoute, ne change pas le cours</t>
+        </is>
+      </c>
+      <c r="AW3" t="inlineStr">
+        <is>
+          <t>narrateur|Il fait froid. Il pleut. Que prend Hermine ?</t>
         </is>
       </c>
     </row>
@@ -1633,6 +1665,11 @@
           <t>confirmation ; le moteur peut dire engine_ok/near avant ce chunk</t>
         </is>
       </c>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>narrateur|Hermine a pris le manteau. Elle a mis les bottes. Papa était là.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1795,6 +1832,11 @@
         <v>8</v>
       </c>
       <c r="AV5" s="2" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>narrateur|Hermine et papa marchent sous la pluie. Les bottes font splish.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1957,6 +1999,11 @@
         <v>8</v>
       </c>
       <c r="AV6" s="2" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>narrateur|L'histoire est finie.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -1975,7 +2022,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A2"/>
+  <dimension ref="A1:A3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -1992,6 +2039,13 @@
       <c r="A2" t="inlineStr">
         <is>
           <t>conversion structurelle, prompts de choix alignés, TTS profilé</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-06.xlsx
@@ -844,7 +844,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AW6"/>
+  <dimension ref="A1:AX6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -1143,6 +1143,11 @@
           <t>script</t>
         </is>
       </c>
+      <c r="AX1" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
@@ -1316,6 +1321,7 @@
 narrateur|Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
         </is>
       </c>
+      <c r="AX2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1503,6 +1509,7 @@
           <t>narrateur|Il fait froid. Il pleut. Que prend Hermine ?</t>
         </is>
       </c>
+      <c r="AX3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1670,6 +1677,7 @@
           <t>narrateur|Hermine a pris le manteau. Elle a mis les bottes. Papa était là.</t>
         </is>
       </c>
+      <c r="AX4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1837,6 +1845,7 @@
           <t>narrateur|Hermine et papa marchent sous la pluie. Les bottes font splish.</t>
         </is>
       </c>
+      <c r="AX5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -2004,6 +2013,7 @@
           <t>narrateur|L'histoire est finie.</t>
         </is>
       </c>
+      <c r="AX6" t="inlineStr"/>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2022,7 +2032,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A3"/>
+  <dimension ref="A1:A5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2046,6 +2056,20 @@
       <c r="A3" t="inlineStr">
         <is>
           <t>F-AUD-006 scripts multi-voix, sans « X dit »</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
         </is>
       </c>
     </row>
@@ -2060,7 +2084,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B15"/>
+  <dimension ref="A1:B16"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="24" customWidth="1" min="1" max="1"/>
@@ -2247,6 +2271,18 @@
         </is>
       </c>
     </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>sons</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>ids de bruits (vide = silence). Le bruit se joue, puis l'histoire reprend au calme.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/stories/arbres/ATOM-TMP.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-06.xlsx
@@ -481,7 +481,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B30"/>
+  <dimension ref="A1:B31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="28" customWidth="1" min="1" max="1"/>
@@ -544,7 +544,7 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Hermine prend manteau et bottes</t>
+          <t>La corbeille vide</t>
         </is>
       </c>
     </row>
@@ -830,6 +830,18 @@
       <c r="B30" t="inlineStr">
         <is>
           <t>voix-roles-v1</t>
+        </is>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>fil_rouge</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>Aniss veut le pain chaud du village. Il pleut. Il prend manteau et bottes. Une flaque barre le chemin. Les bottes font splish. Le pain rentre dans la corbeille.</t>
         </is>
       </c>
     </row>
@@ -1172,12 +1184,12 @@
       </c>
       <c r="E2" s="2" t="inlineStr">
         <is>
-          <t>Hermine est dans l'entrée. Papa ouvre la porte. L'air est froid. Froid, manteau. Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence. Pluie, bottes. Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip. Froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble. Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
+          <t>La corbeille à pain est encore vide. Elle attend sur la table de bois. Une miette sèche y reste, toute seule. Il n'y a plus de pain, Aniss. On va en chercher ? Oui. Chez le boulanger. Dehors, la pluie tape le volet. Le volet claque un peu. L'air qui entre est froid. Il pique les joues. J'ai froid aux mains. Tu prends le manteau. Il fait froid. Le manteau bleu pend au crochet. Aniss le prend. Il glisse la manche gauche. Puis la droite. Le tissu est un peu rêche, déjà chaud. Le zip, tout doux. Papa ferme le zip. Ça fait zzz. Je suis au chaud. Il pleut aussi. Tu mets les bottes. Les bottes jaunes attendent près du paillasson. Le paillasson est déjà mouillé. Aniss pose le pied gauche. La botte colle un peu. Puis le pied droit. Elles sont jaunes. Oui. Tes pieds resteront au sec. Tu as tes bottes ? Oui, papa. En ce moment, papa ouvre la porte. La pluie sent la terre. L'eau court dans le zinc. Ça chante. C'est la pluie. Ils marchent vers le village. Le chemin brille. Une grande flaque barre le passage. Une mer ! Une flaque. On la contourne ? Je peux dessus. Avec tes bottes, oui.</t>
         </is>
       </c>
       <c r="F2" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hermine est dans l'entrée. Papa ouvre la porte. L'air est &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Papa dit : froid, manteau. Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence. Papa dit : pluie, bottes. Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip. Hermine dit : froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble. Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.&lt;/prosody&gt;&lt;break time="400ms"/&gt;&lt;/speak&gt;</t>
+          <t>La corbeille à pain est encore vide. Elle attend sur la table de bois. Une miette sèche y reste, toute seule. Il n'y a plus de pain, Aniss. On va en chercher ? Oui. Chez le boulanger. Dehors, la pluie tape le volet. Le volet claque un peu. L'air qui entre est froid. Il pique les joues. J'ai froid aux mains. Tu prends le manteau. Il fait froid. Le manteau bleu pend au crochet. Aniss le prend. Il glisse la manche gauche. Puis la droite. Le tissu est un peu rêche, déjà chaud. Le zip, tout doux. Papa ferme le zip. Ça fait zzz. Je suis au chaud. Il pleut aussi. Tu mets les bottes. Les bottes jaunes attendent près du paillasson. Le paillasson est déjà mouillé. Aniss pose le pied gauche. La botte colle un peu. Puis le pied droit. Elles sont jaunes. Oui. Tes pieds resteront au sec. Tu as tes bottes ? Oui, papa. En ce moment, papa ouvre la porte. La pluie sent la terre. L'eau court dans le zinc. Ça chante. C'est la pluie. Ils marchent vers le village. Le chemin brille. Une grande flaque barre le passage. Une mer ! Une flaque. On la contourne ? Je peux dessus. Avec tes bottes, oui.</t>
         </is>
       </c>
       <c r="G2" s="2" t="inlineStr">
@@ -1240,7 +1252,7 @@
         <v>0.92</v>
       </c>
       <c r="AB2" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC2" s="2" t="inlineStr">
         <is>
@@ -1312,16 +1324,56 @@
       <c r="AV2" s="2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>narrateur|Hermine est dans l'entrée. Papa ouvre la porte. L'air est froid.
-papa|Froid, manteau.
-narrateur|Hermine prend le manteau. Elle enfile les manches. Le manteau est chaud. Dehors, la pluie commence.
-papa|Pluie, bottes.
-narrateur|Hermine met les bottes. Les bottes sont jaunes. Elle entend la pluie sur le toit. Papa ferme le zip.
-enfant-f|Froid, manteau. Pluie, bottes. Papa hoche la tête. Ils sortent ensemble.
-narrateur|Les gouttes tombent sur le manteau. Les pieds restent au sec. Hermine sourit. Papa tient la main.</t>
-        </is>
-      </c>
-      <c r="AX2" t="inlineStr"/>
+          <t>narrateur|La corbeille à pain est encore vide.
+narrateur|Elle attend sur la table de bois.
+narrateur|Une miette sèche y reste, toute seule.
+papa|Il n'y a plus de pain, Aniss.
+enfant-m|On va en chercher ?
+papa|Oui.
+papa|Chez le boulanger.
+narrateur|Dehors, la pluie tape le volet.
+narrateur|Le volet claque un peu.
+narrateur|L'air qui entre est froid.
+narrateur|Il pique les joues.
+enfant-m|J'ai froid aux mains.
+papa|Tu prends le manteau.
+papa|Il fait froid.
+narrateur|Le manteau bleu pend au crochet.
+narrateur|Aniss le prend.
+narrateur|Il glisse la manche gauche.
+narrateur|Puis la droite.
+narrateur|Le tissu est un peu rêche, déjà chaud.
+papa|Le zip, tout doux.
+narrateur|Papa ferme le zip.
+narrateur|Ça fait zzz.
+enfant-m|Je suis au chaud.
+papa|Il pleut aussi.
+papa|Tu mets les bottes.
+narrateur|Les bottes jaunes attendent près du paillasson.
+narrateur|Le paillasson est déjà mouillé.
+narrateur|Aniss pose le pied gauche.
+narrateur|La botte colle un peu.
+narrateur|Puis le pied droit.
+enfant-m|Elles sont jaunes.
+papa|Oui.
+papa|Tes pieds resteront au sec.
+papa|Tu as tes bottes ?
+enfant-m|Oui, papa.
+narrateur|En ce moment, papa ouvre la porte.
+narrateur|La pluie sent la terre.
+narrateur|L'eau court dans le zinc.
+enfant-m|Ça chante.
+papa|C'est la pluie.
+narrateur|Ils marchent vers le village.
+narrateur|Le chemin brille.
+narrateur|Une grande flaque barre le passage.
+enfant-m|Une mer !
+papa|Une flaque.
+papa|On la contourne ?
+enfant-m|Je peux dessus.
+papa|Avec tes bottes, oui.</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -1346,12 +1398,12 @@
       </c>
       <c r="E3" s="2" t="inlineStr">
         <is>
-          <t>Il fait froid. Il pleut. Que prend Hermine ?</t>
+          <t>Il fait froid. Il pleut. Que prend Aniss ?</t>
         </is>
       </c>
       <c r="F3" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="medium"&gt;Il fait &lt;emphasis level="moderate"&gt;froid&lt;/emphasis&gt;. Il pleut. Que prend Hermine ?&lt;/prosody&gt;&lt;break time="250ms"/&gt;&lt;/speak&gt;</t>
+          <t>Il fait froid. Il pleut. Que prend Aniss ?</t>
         </is>
       </c>
       <c r="G3" s="2" t="inlineStr">
@@ -1381,7 +1433,7 @@
       </c>
       <c r="L3" s="2" t="inlineStr">
         <is>
-          <t>Froid, manteau. Pluie, bottes. Que prend-elle ?</t>
+          <t>Froid, manteau. Pluie, bottes. Que prend-il ?</t>
         </is>
       </c>
       <c r="M3" s="2" t="inlineStr"/>
@@ -1430,7 +1482,7 @@
         <v>0.86</v>
       </c>
       <c r="AB3" s="2" t="n">
-        <v>1.3</v>
+        <v>1.28</v>
       </c>
       <c r="AC3" s="2" t="inlineStr">
         <is>
@@ -1506,10 +1558,11 @@
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>narrateur|Il fait froid. Il pleut. Que prend Hermine ?</t>
-        </is>
-      </c>
-      <c r="AX3" t="inlineStr"/>
+          <t>narrateur|Il fait froid.
+narrateur|Il pleut.
+narrateur|Que prend Aniss ?</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -1534,12 +1587,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>Hermine a pris le manteau. Elle a mis les bottes. Papa était là.</t>
+          <t>Aniss pose un pied dans l'eau. Ça fait splish. L'eau monte un peu. Elle n'entre pas. Mes pieds sont au sec ! Le manteau te tient chaud. Les bottes te tiennent au sec. Il pose l'autre pied. Splish encore. Une feuille tourne dans la flaque. Elle nage. On continue. Le pain nous attend. Le village sent la farine mouillée. La vitrine de la boulangerie est embuée. Je vois le pain ! Il est tout chaud. Papa pousse la porte. Une clochette sonne. L'air dedans sent le four.</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hermine a pris le manteau. Elle a mis les bottes. Papa était là.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Aniss pose un pied dans l'eau. Ça fait splish. L'eau monte un peu. Elle n'entre pas. Mes pieds sont au sec ! Le manteau te tient chaud. Les bottes te tiennent au sec. Il pose l'autre pied. Splish encore. Une feuille tourne dans la flaque. Elle nage. On continue. Le pain nous attend. Le village sent la farine mouillée. La vitrine de la boulangerie est embuée. Je vois le pain ! Il est tout chaud. Papa pousse la porte. Une clochette sonne. L'air dedans sent le four.</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -1602,7 +1655,7 @@
         <v>0.92</v>
       </c>
       <c r="AB4" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC4" s="2" t="inlineStr">
         <is>
@@ -1674,10 +1727,28 @@
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>narrateur|Hermine a pris le manteau. Elle a mis les bottes. Papa était là.</t>
-        </is>
-      </c>
-      <c r="AX4" t="inlineStr"/>
+          <t>narrateur|Aniss pose un pied dans l'eau.
+narrateur|Ça fait splish.
+narrateur|L'eau monte un peu.
+narrateur|Elle n'entre pas.
+enfant-m|Mes pieds sont au sec !
+papa|Le manteau te tient chaud.
+papa|Les bottes te tiennent au sec.
+narrateur|Il pose l'autre pied.
+narrateur|Splish encore.
+narrateur|Une feuille tourne dans la flaque.
+enfant-m|Elle nage.
+papa|On continue.
+papa|Le pain nous attend.
+narrateur|Le village sent la farine mouillée.
+narrateur|La vitrine de la boulangerie est embuée.
+enfant-m|Je vois le pain !
+papa|Il est tout chaud.
+narrateur|Papa pousse la porte.
+narrateur|Une clochette sonne.
+narrateur|L'air dedans sent le four.</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -1702,12 +1773,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>Hermine et papa marchent sous la pluie. Les bottes font splish.</t>
+          <t>Le boulanger tend un pain doré. La croûte craque un peu. Il est lourd. Tu le portes ? Oui. Aniss serre le pain contre le manteau. Le pain chauffe le tissu. Merci, Aniss. Tu tiens bien. Ils retraversent la rue brillante. La flaque est encore là. Splish ! Tes bottes travaillent. Une goutte glisse sur le pain. Aniss le cache un peu. Le manteau le garde. Il reste chaud. La maison se rapproche. Le volet claque encore, plus doux.</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="medium" pitch="medium"&gt;Hermine et papa marchent sous la &lt;emphasis level="moderate"&gt;pluie&lt;/emphasis&gt;. Les bottes font splish.&lt;/prosody&gt;&lt;break time="450ms"/&gt;&lt;/speak&gt;</t>
+          <t>Le boulanger tend un pain doré. La croûte craque un peu. Il est lourd. Tu le portes ? Oui. Aniss serre le pain contre le manteau. Le pain chauffe le tissu. Merci, Aniss. Tu tiens bien. Ils retraversent la rue brillante. La flaque est encore là. Splish ! Tes bottes travaillent. Une goutte glisse sur le pain. Aniss le cache un peu. Le manteau le garde. Il reste chaud. La maison se rapproche. Le volet claque encore, plus doux.</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1770,7 +1841,7 @@
         <v>0.92</v>
       </c>
       <c r="AB5" s="2" t="n">
-        <v>1.18</v>
+        <v>1.22</v>
       </c>
       <c r="AC5" s="2" t="inlineStr">
         <is>
@@ -1842,10 +1913,27 @@
       <c r="AV5" s="2" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>narrateur|Hermine et papa marchent sous la pluie. Les bottes font splish.</t>
-        </is>
-      </c>
-      <c r="AX5" t="inlineStr"/>
+          <t>narrateur|Le boulanger tend un pain doré.
+narrateur|La croûte craque un peu.
+enfant-m|Il est lourd.
+papa|Tu le portes ?
+enfant-m|Oui.
+narrateur|Aniss serre le pain contre le manteau.
+narrateur|Le pain chauffe le tissu.
+papa|Merci, Aniss.
+papa|Tu tiens bien.
+narrateur|Ils retraversent la rue brillante.
+narrateur|La flaque est encore là.
+enfant-m|Splish !
+papa|Tes bottes travaillent.
+narrateur|Une goutte glisse sur le pain.
+narrateur|Aniss le cache un peu.
+papa|Le manteau le garde.
+enfant-m|Il reste chaud.
+narrateur|La maison se rapproche.
+narrateur|Le volet claque encore, plus doux.</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -1870,12 +1958,12 @@
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>L'histoire est finie.</t>
+          <t>Papa ouvre la porte. L'odeur du pain entre avant eux. Aniss pose le pain dans la corbeille. La corbeille n'est plus vide. Il est rentré. Oui. Tu poses les bottes ? Les bottes gouttent près du paillasson. Le manteau s'égoutte au crochet. Une miette chaude reste sur la table. Je la prends. Elle est à toi. Dehors, la flaque brille encore. Dedans, le pain sent le four.</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>&lt;speak&gt;&lt;prosody rate="slow" pitch="low"&gt;L'histoire est finie.&lt;/prosody&gt;&lt;break time="600ms"/&gt;&lt;/speak&gt;</t>
+          <t>Papa ouvre la porte. L'odeur du pain entre avant eux. Aniss pose le pain dans la corbeille. La corbeille n'est plus vide. Il est rentré. Oui. Tu poses les bottes ? Les bottes gouttent près du paillasson. Le manteau s'égoutte au crochet. Une miette chaude reste sur la table. Je la prends. Elle est à toi. Dehors, la flaque brille encore. Dedans, le pain sent le four.</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1931,14 +2019,14 @@
       </c>
       <c r="Z6" s="2" t="inlineStr">
         <is>
-          <t>slow</t>
+          <t>medium</t>
         </is>
       </c>
       <c r="AA6" s="2" t="n">
         <v>0.88</v>
       </c>
       <c r="AB6" s="2" t="n">
-        <v>1.26</v>
+        <v>1.22</v>
       </c>
       <c r="AC6" s="2" t="inlineStr">
         <is>
@@ -2010,10 +2098,22 @@
       <c r="AV6" s="2" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>narrateur|L'histoire est finie.</t>
-        </is>
-      </c>
-      <c r="AX6" t="inlineStr"/>
+          <t>narrateur|Papa ouvre la porte.
+narrateur|L'odeur du pain entre avant eux.
+narrateur|Aniss pose le pain dans la corbeille.
+narrateur|La corbeille n'est plus vide.
+enfant-m|Il est rentré.
+papa|Oui.
+papa|Tu poses les bottes ?
+narrateur|Les bottes gouttent près du paillasson.
+narrateur|Le manteau s'égoutte au crochet.
+narrateur|Une miette chaude reste sur la table.
+enfant-m|Je la prends.
+papa|Elle est à toi.
+narrateur|Dehors, la flaque brille encore.
+narrateur|Dedans, le pain sent le four.</t>
+        </is>
+      </c>
     </row>
   </sheetData>
   <autoFilter ref="A1:AV6"/>
@@ -2032,7 +2132,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A5"/>
+  <dimension ref="A1:A6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="100" customWidth="1" min="1" max="1"/>
@@ -2070,6 +2170,13 @@
       <c r="A5" t="inlineStr">
         <is>
           <t>F-AUD-007 colonne sons ; vide = silence ; jamais parler dans le bruit</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>F-NAR-008 récit, pas une leçon en puces</t>
         </is>
       </c>
     </row>

--- a/stories/arbres/ATOM-TMP.MET.001-06.xlsx
+++ b/stories/arbres/ATOM-TMP.MET.001-06.xlsx
@@ -671,7 +671,7 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>entrée</t>
+          <t>maison, rue du village sous la pluie, boulangerie</t>
         </is>
       </c>
     </row>
@@ -683,7 +683,7 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>Hermine, papa</t>
+          <t>Aniss, papa</t>
         </is>
       </c>
     </row>
